--- a/satisfaction_surveys/002_educational_kit_evaluation_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/002_educational_kit_evaluation_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not At All Likely'}</t>
+          <t>Not At All Likely</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'1-3'}</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '1-3'}</t>
+          <t>1-3</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'1-6'}</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '1-6'}</t>
+          <t>1-6</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'7_or_more'}</t>
+          <t>7_or_more</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '7 or more'}</t>
+          <t>7 or more</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_worthwhile'}</t>
+          <t>not_worthwhile</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not Worthwhile'}</t>
+          <t>Not Worthwhile</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_worthwhile'}</t>
+          <t>not_very_worthwhile</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Worthwhile'}</t>
+          <t>Not Very Worthwhile</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_worthwhile'}</t>
+          <t>somewhat_worthwhile</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Worthwhile'}</t>
+          <t>Somewhat Worthwhile</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_worthwhile'}</t>
+          <t>very_worthwhile</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very Worthwhile'}</t>
+          <t>Very Worthwhile</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_worthwhile'}</t>
+          <t>extremely_worthwhile</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely Worthwhile'}</t>
+          <t>Extremely Worthwhile</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_satisfied'}</t>
+          <t>extremely_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely Satisfied'}</t>
+          <t>Extremely Satisfied</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'not_recommended'}</t>
+          <t>not_recommended</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Not Recommended'}</t>
+          <t>Not Recommended</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'recommended'}</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Recommended'}</t>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'not_recommended_to_anyone'}</t>
+          <t>not_recommended_to_anyone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Not Recommended to Anyone'}</t>
+          <t>Not Recommended to Anyone</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'recommended_to_a_few'}</t>
+          <t>recommended_to_a_few</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Recommended to a Few'}</t>
+          <t>Recommended to a Few</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'recommended_to_many'}</t>
+          <t>recommended_to_many</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Recommended to Many'}</t>
+          <t>Recommended to Many</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'recommended_to_all'}</t>
+          <t>recommended_to_all</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Recommended to All'}</t>
+          <t>Recommended to All</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'not_helpful'}</t>
+          <t>not_helpful</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Not Helpful'}</t>
+          <t>Not Helpful</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_helpful'}</t>
+          <t>somewhat_helpful</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Helpful'}</t>
+          <t>Somewhat Helpful</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'very_helpful'}</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Very Helpful'}</t>
+          <t>Very Helpful</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_helpful'}</t>
+          <t>extremely_helpful</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely Helpful'}</t>
+          <t>Extremely Helpful</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'not_helpful_to_anyone'}</t>
+          <t>not_helpful_to_anyone</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Not Helpful to Anyone'}</t>
+          <t>Not Helpful to Anyone</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'helpful_to_a_few'}</t>
+          <t>helpful_to_a_few</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Helpful to a Few'}</t>
+          <t>Helpful to a Few</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'helpful_to_many'}</t>
+          <t>helpful_to_many</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Helpful to Many'}</t>
+          <t>Helpful to Many</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'helpful_to_all'}</t>
+          <t>helpful_to_all</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Helpful to All'}</t>
+          <t>Helpful to All</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'not_improve'}</t>
+          <t>not_improve</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Not Improve'}</t>
+          <t>Not Improve</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_improve'}</t>
+          <t>somewhat_improve</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Improve'}</t>
+          <t>Somewhat Improve</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'very_improve'}</t>
+          <t>very_improve</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Very Improve'}</t>
+          <t>Very Improve</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_improve'}</t>
+          <t>extremely_improve</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely Improve'}</t>
+          <t>Extremely Improve</t>
         </is>
       </c>
     </row>
